--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,34 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s01.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ea09ff500520c925feb6b990a99b603149ec211af40c974af601f54e5c7cfe34</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S01.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,34 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s02.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4d4311796be765c1e2a223719ff4549ab663838a3fcbc051ea85e2e2a655909c</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S02.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,34 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s03.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0d1d5ed79c00fde7fbd0f40ae9906c1e809198a79a8e1c94fc51fa4ceb771829</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S03.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,6 +824,34 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s04.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>453a98b3dec527ba611ccb4138e69af7686f68e72194479769300ac6e7963ef8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Committed exact public level-curve numeric anchors for Goal 07 S04.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +852,34 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s05.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S05.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,34 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s06.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S06.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,34 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s07.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S07.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,34 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s08.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S08.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,34 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s09.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S09.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,34 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s10.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S10.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,34 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s11.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S11.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,34 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s12.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>14</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S12.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,34 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s13.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S13.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1104,34 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s14.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S14.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,6 +1132,34 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s15.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S15.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1160,34 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s16.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S16.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1188,34 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s17.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>66e4eb362380a285caf0a06a360629ab8895fc6a30bd63e1a9dea34897edad82</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S17.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,6 +1216,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s18.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S18.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,510 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s01.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ea09ff500520c925feb6b990a99b603149ec211af40c974af601f54e5c7cfe34</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s02.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4d4311796be765c1e2a223719ff4549ab663838a3fcbc051ea85e2e2a655909c</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s03.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0d1d5ed79c00fde7fbd0f40ae9906c1e809198a79a8e1c94fc51fa4ceb771829</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s04.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>453a98b3dec527ba611ccb4138e69af7686f68e72194479769300ac6e7963ef8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Committed exact public level-curve numeric anchors for Goal 07 S04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s05.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s06.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s07.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s08.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s09.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s10.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s11.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s12.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>14</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s13.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s14.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s15.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s16.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s17.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>66e4eb362380a285caf0a06a360629ab8895fc6a30bd63e1a9dea34897edad82</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>evidence.goal07.enemy.s18.numeric-anchors</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SourcePayload</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Committed per-variant numeric anchors for Goal 07 S18.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EvidenceRecord.xlsx
+++ b/config/data/EvidenceRecord.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EvidenceRecord" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EvidenceRecord" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,240 +499,255 @@
   </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="5" min="2" max="3"/>
+    <col width="18.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="30.7109375" customWidth="1" style="5" min="5" max="5"/>
+    <col width="12.7109375" customWidth="1" style="5" min="6" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>EvidenceRecord</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>9a747b9aebbc300d</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>5400673caa2e0bdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>source_record_id</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>source_record_id</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;EvidenceKind&gt;</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>optional&lt;ref&lt;SourceRecord.id&gt;&gt;</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key;range=1..2147483647</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>length=1..160</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>length=64..64</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>length=1..1000</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -731,18 +831,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0dca8ae581b4fa1e9fe8ce0c9e67ac6eb72c251deacbd4831751ce685e45ef5a</t>
+          <t>b237477309589c82a3866e553d8cdf4486f7027c25fb95ae7bf633f539424a7c</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Deterministically normalized Version 4.4 reference pack used by executable Standard-v1 rows.</t>
+          <t>Deterministically normalized current Version 4.4 reference pack used by production rows.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>4</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -754,8 +856,10 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -769,8 +873,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>5</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -782,8 +888,10 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -797,8 +905,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>6</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -810,8 +920,10 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>5</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -825,8 +937,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>7</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -838,8 +952,10 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>6</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -853,12 +969,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>8</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s05.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s07.numeric-anchors</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -866,27 +984,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>7</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
+          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S05.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S07.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>9</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s06.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s08.numeric-anchors</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -894,27 +1016,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>8</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
+          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S06.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S08.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>10</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s07.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s09.numeric-anchors</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -922,27 +1048,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>9</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5d9b55cfcf3785dfa5ebdd490c94159a73152c1a7b606eb73fbe3d59701cdd8c</t>
+          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S07.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S09.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>11</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s08.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s10.numeric-anchors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -950,27 +1080,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>10</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2e12722a69ed4d9e3505ab976461a8ffff488882066dc5e110c2596108b120e4</t>
+          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S08.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S10.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>12</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s09.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s11.numeric-anchors</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -978,27 +1112,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>11</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>baf95718a79bf0cf1e26b72e6c8a96b3388435b5891293572c9ab7688610c37b</t>
+          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S09.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S11.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>13</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s10.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s12.numeric-anchors</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1006,27 +1144,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>12</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0c1f380b815886649d1ed34a2008be533b7bcbf815f76697f200fe4d4ea0a978</t>
+          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S10.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S12.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>14</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s11.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s13.numeric-anchors</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1034,27 +1176,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>13</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9dd5d4bd0d456367cb33a419d075adb6bc1803885288628edb5c0a1a700cd50a</t>
+          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Committed exact public per-level numeric anchors for Goal 07 S11.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S13.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>15</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s12.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s14.numeric-anchors</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1062,27 +1208,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>14</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30e9da848659c264b4cd88dbefb5184f6cef8dbcfb0da28b96366c8ff23dc2d8</t>
+          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S12.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S14.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>16</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s13.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s15.numeric-anchors</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1090,27 +1240,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>15</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>b8ac0544918a16ec2aa1fdeb44710d56d34c440f6e7d7670a5ad5378b2980d60</t>
+          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S13.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S15.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>17</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s14.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s16.numeric-anchors</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1118,27 +1272,31 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>16</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7029ace9aa6d914df71837fcaf80b7835e391c3dc4bb3a7d6184cbcb0eb7c16d</t>
+          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S14.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S16.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>18</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s15.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s18.numeric-anchors</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1146,27 +1304,29 @@
           <t>SourcePayload</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>17</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1c72ae67bc8824ec64eb8d32020d56ca828f8acae2965c1b142df2c40e9cac5b</t>
+          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S15.</t>
+          <t>Committed per-variant numeric anchors for Goal 07 S18.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s16.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s05.numeric-anchors</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1175,16 +1335,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>cfd5c01eaa2ea61c4794d090b3fc4a840ed303ebbdb98ce9134378227be4bcb7</t>
+          <t>26675eafbb7481936c53e20fcc1a6ea7ae50a79452be337ed618da75fb7d753b</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S16.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S05.</t>
         </is>
       </c>
     </row>
@@ -1218,11 +1378,11 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>evidence.goal07.enemy.s18.numeric-anchors</t>
+          <t>evidence.goal07.enemy.s06.numeric-anchors</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1231,20 +1391,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fd4802d9930af4aaddb2a6a9d843574536cfea13ee2dc651fc3f304f571dba31</t>
+          <t>c7e7d2b355406f348aca7e306725669a35231c556d4656553a567d58df4b0525</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Committed per-variant numeric anchors for Goal 07 S18.</t>
+          <t>Committed exact public per-level numeric anchors for Goal 07 S06.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: SourcePayload, ReleasedText, Observation, GoldenFixture, ProjectPolicy" promptTitle="EvidenceKind enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"SourcePayload,ReleasedText,Observation,GoldenFixture,ProjectPolicy"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>